--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2025.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/sep-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -753,7 +753,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -766,7 +770,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>624-247-CM25</t>
+          <t>688-173-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -791,43 +795,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>61.301.100-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>14283.99</v>
+        <v>71582.07000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2429-2562-CM25</t>
+          <t>4044-655-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -847,48 +855,52 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.061.800-1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8205.219999999999</v>
+        <v>53116.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057494-8528-CM25</t>
+          <t>2598-180-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -913,43 +925,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.608.102-0</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>71651.33</v>
+        <v>4711.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>812261-5158-CM25</t>
+          <t>2429-2563-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -969,22 +985,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -997,20 +1013,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9516.370000000001</v>
+        <v>29304.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2429-2563-CM25</t>
+          <t>3705-413-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1035,43 +1055,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>29304.35</v>
+        <v>15393.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3705-413-CM25</t>
+          <t>1057494-8528-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1096,27 +1120,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>61.608.102-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1126,13 +1150,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>15393.84</v>
+        <v>71651.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2598-180-CM25</t>
+          <t>2429-2562-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1157,43 +1181,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4711.35</v>
+        <v>8205.219999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4044-655-CM25</t>
+          <t>624-247-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1218,43 +1246,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.061.800-1</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE PASCUA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>53116.25</v>
+        <v>14283.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>688-173-CM25</t>
+          <t>812261-5158-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1279,12 +1311,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.301.100-5</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>OFICINA DE ESTUDIOS Y POLITICAS AGRARIAS</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1294,22 +1326,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>71582.07000000001</v>
+        <v>9516.370000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1363,7 +1399,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1376,7 +1416,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>622-543-CM25</t>
+          <t>752-374-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1396,48 +1436,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>26892.81</v>
+        <v>36945.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>752-374-CM25</t>
+          <t>618923-218-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1457,32 +1501,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.979.970-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1492,13 +1536,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>36945.22</v>
+        <v>185452.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>618923-218-CM25</t>
+          <t>797305-87-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1523,12 +1567,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.979.970-4</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1538,28 +1582,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>880443249</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>185452.93</v>
+        <v>75963.64999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>797305-87-CM25</t>
+          <t>622-543-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1584,12 +1632,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1599,12 +1647,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1618,13 +1666,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>75963.64999999999</v>
+        <v>26892.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2409-1257-CM25</t>
+          <t>4290-116-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1649,27 +1697,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1679,13 +1727,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>22193.5</v>
+        <v>7735</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3756-627-CM25</t>
+          <t>2409-1257-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1705,48 +1753,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11584.65</v>
+        <v>22193.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4290-116-CM25</t>
+          <t>3756-627-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,42 +1818,46 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7735</v>
+        <v>11584.65</v>
       </c>
     </row>
     <row r="23">
@@ -1855,7 +1911,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1868,7 +1928,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3904-1208-CM25</t>
+          <t>1121-93-SE25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1883,53 +1943,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>96.826.830-9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2114.75</v>
+        <v>30696.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>980-225-CM25</t>
+          <t>3181-407-SE25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1944,22 +2008,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1969,28 +2033,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>22587.39</v>
+        <v>244188</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1223542-306-CM25</t>
+          <t>3904-1208-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2005,53 +2073,57 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.104.928-8</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1480.32</v>
+        <v>2114.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057492-5974-CM25</t>
+          <t>980-225-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,22 +2138,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2091,28 +2163,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>46838.4</v>
+        <v>22587.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1271178-319-CM25</t>
+          <t>1057492-5974-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2127,7 +2203,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2137,12 +2213,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>71.369.900-4</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2152,12 +2228,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2167,13 +2243,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1281.63</v>
+        <v>46838.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1375746-55-CM25</t>
+          <t>1223542-306-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2188,7 +2264,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2198,43 +2274,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.981.280-8</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>13907.53</v>
+        <v>1480.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>859378-575-CM25</t>
+          <t>1271178-319-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2249,7 +2329,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2259,43 +2339,47 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>71.369.900-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL DE MACUL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>59500</v>
+        <v>1281.63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4513-137-CM25</t>
+          <t>1375746-55-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2310,53 +2394,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>61.981.280-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.288.338-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10364.9</v>
+        <v>13907.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5586-2981-CM25</t>
+          <t>859378-575-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2376,48 +2464,52 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>68130.25999999999</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057500-592-CM25</t>
+          <t>4513-137-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2432,53 +2524,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4618.15</v>
+        <v>10364.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2446-1601-CM25</t>
+          <t>5586-2981-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2493,7 +2589,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2503,27 +2599,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2537,13 +2633,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>806820</v>
+        <v>68130.25999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1347870-167-CM25</t>
+          <t>1057500-592-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2558,7 +2654,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2568,43 +2664,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>29606.49</v>
+        <v>4618.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3479-1655-CM25</t>
+          <t>2446-1601-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2619,7 +2719,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2629,97 +2729,231 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2069.65</v>
+        <v>806820</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>1347870-167-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>29606.49</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3479-1655-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>2069.65</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>1725-5533-CM25</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>sep-2025</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>60.901.002-9</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>MSLI Latam Inc.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>880443249</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
         <v>346215.74</v>
       </c>
     </row>
